--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>136193852</v>
       </c>
       <c r="B11" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>136193852</v>
       </c>
       <c r="B11" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>136193852</v>
       </c>
       <c r="B11" t="n">
-        <v>99368</v>
+        <v>99373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 22067-2024 artfynd.xlsx
+++ b/artfynd/A 22067-2024 artfynd.xlsx
@@ -1601,7 +1601,7 @@
         <v>136193852</v>
       </c>
       <c r="B11" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
